--- a/AAII_Financials/Quarterly/AIU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AIU_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
   <si>
     <t>AIU</t>
   </si>
@@ -656,7 +656,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -665,178 +665,203 @@
     <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="7" max="8" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45169</v>
+      </c>
+      <c r="E7" s="2">
+        <v>44985</v>
+      </c>
+      <c r="F7" s="2">
         <v>44804</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>44620</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44439</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44255</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44165</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44074</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>43982</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>43890</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>43799</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43708</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43616</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2000</v>
+        <v>19400</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="F8" s="3">
-        <v>472700</v>
+        <v>2100</v>
       </c>
       <c r="G8" s="3">
-        <v>128600</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3">
-        <v>94600</v>
+        <v>0</v>
       </c>
       <c r="I8" s="3">
+        <v>931600</v>
+      </c>
+      <c r="J8" s="3">
+        <v>684800</v>
+      </c>
+      <c r="K8" s="3">
         <v>139600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>102900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>123300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>116400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>193200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>161100</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1800</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>8</v>
+        <v>9800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>7200</v>
       </c>
       <c r="F9" s="3">
-        <v>289100</v>
-      </c>
-      <c r="G9" s="3">
-        <v>74900</v>
-      </c>
-      <c r="H9" s="3">
-        <v>65800</v>
+        <v>1900</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I9" s="3">
+        <v>542500</v>
+      </c>
+      <c r="J9" s="3">
+        <v>476500</v>
+      </c>
+      <c r="K9" s="3">
         <v>88500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>66600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>73700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>75400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>98300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>79900</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>300</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>8</v>
+        <v>9600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5800</v>
       </c>
       <c r="F10" s="3">
-        <v>183600</v>
-      </c>
-      <c r="G10" s="3">
-        <v>53700</v>
-      </c>
-      <c r="H10" s="3">
-        <v>28800</v>
+        <v>200</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I10" s="3">
+        <v>389100</v>
+      </c>
+      <c r="J10" s="3">
+        <v>208300</v>
+      </c>
+      <c r="K10" s="3">
         <v>51100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>36200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>49600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>41000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>94900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>81200</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -851,8 +876,10 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -889,8 +916,14 @@
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -927,8 +960,14 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -965,8 +1004,14 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1003,8 +1048,14 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1016,84 +1067,98 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2800</v>
+        <v>10700</v>
       </c>
       <c r="E17" s="3">
-        <v>49800</v>
+        <v>8100</v>
       </c>
       <c r="F17" s="3">
-        <v>1144100</v>
+        <v>-1800</v>
       </c>
       <c r="G17" s="3">
-        <v>143900</v>
+        <v>57100</v>
       </c>
       <c r="H17" s="3">
-        <v>117100</v>
+        <v>9700</v>
       </c>
       <c r="I17" s="3">
+        <v>1042000</v>
+      </c>
+      <c r="J17" s="3">
+        <v>848300</v>
+      </c>
+      <c r="K17" s="3">
         <v>155600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>113500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>130900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>133200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>182000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>143000</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-700</v>
+        <v>8700</v>
       </c>
       <c r="E18" s="3">
-        <v>-49800</v>
+        <v>4900</v>
       </c>
       <c r="F18" s="3">
-        <v>-671400</v>
+        <v>3900</v>
       </c>
       <c r="G18" s="3">
-        <v>-15200</v>
+        <v>-57100</v>
       </c>
       <c r="H18" s="3">
-        <v>-22600</v>
+        <v>-9700</v>
       </c>
       <c r="I18" s="3">
+        <v>-110400</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-163500</v>
+      </c>
+      <c r="K18" s="3">
         <v>-16000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-10700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-7600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-16700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>11200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1108,46 +1173,54 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>-3200</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>2100</v>
+        <v>600</v>
       </c>
       <c r="I20" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="J20" s="3">
+        <v>15500</v>
+      </c>
+      <c r="K20" s="3">
         <v>-5500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-47500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>4300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>4600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>9900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1157,8 +1230,8 @@
       <c r="E21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="3">
-        <v>-650700</v>
+      <c r="F21" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>8</v>
@@ -1178,128 +1251,152 @@
       <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="3">
         <v>47000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>5500</v>
+        <v>900</v>
       </c>
       <c r="E22" s="3">
-        <v>1500</v>
+        <v>2900</v>
       </c>
       <c r="F22" s="3">
-        <v>13600</v>
+        <v>5700</v>
       </c>
       <c r="G22" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H22" s="3">
+        <v>7900</v>
+      </c>
+      <c r="I22" s="3">
+        <v>27400</v>
+      </c>
+      <c r="J22" s="3">
+        <v>26100</v>
+      </c>
+      <c r="K22" s="3">
+        <v>4200</v>
+      </c>
+      <c r="L22" s="3">
+        <v>3900</v>
+      </c>
+      <c r="M22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="N22" s="3">
         <v>3800</v>
       </c>
-      <c r="H22" s="3">
-        <v>3600</v>
-      </c>
-      <c r="I22" s="3">
-        <v>4200</v>
-      </c>
-      <c r="J22" s="3">
-        <v>3900</v>
-      </c>
-      <c r="K22" s="3">
-        <v>2700</v>
-      </c>
-      <c r="L22" s="3">
-        <v>3800</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>3000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-6300</v>
+        <v>8500</v>
       </c>
       <c r="E23" s="3">
-        <v>-51400</v>
+        <v>2000</v>
       </c>
       <c r="F23" s="3">
-        <v>-688200</v>
+        <v>-1700</v>
       </c>
       <c r="G23" s="3">
-        <v>-22000</v>
+        <v>-58800</v>
       </c>
       <c r="H23" s="3">
-        <v>-24000</v>
+        <v>-17000</v>
       </c>
       <c r="I23" s="3">
+        <v>-159700</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-174100</v>
+      </c>
+      <c r="K23" s="3">
         <v>-25700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-62100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-6000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-15900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>18100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>22000</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F24" s="3">
-        <v>4300</v>
+        <v>0</v>
       </c>
       <c r="G24" s="3">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="H24" s="3">
-        <v>-1700</v>
+        <v>30900</v>
       </c>
       <c r="I24" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="J24" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="K24" s="3">
         <v>-1500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-2900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>6500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1336,84 +1433,102 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-6300</v>
+        <v>8500</v>
       </c>
       <c r="E26" s="3">
-        <v>-51400</v>
+        <v>2000</v>
       </c>
       <c r="F26" s="3">
-        <v>-692400</v>
+        <v>-1700</v>
       </c>
       <c r="G26" s="3">
-        <v>-21100</v>
+        <v>-58800</v>
       </c>
       <c r="H26" s="3">
-        <v>-22300</v>
+        <v>-17000</v>
       </c>
       <c r="I26" s="3">
+        <v>-152600</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-161800</v>
+      </c>
+      <c r="K26" s="3">
         <v>-24200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-61800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-3000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-15500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>11600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>15100</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-7600</v>
+        <v>8500</v>
       </c>
       <c r="E27" s="3">
-        <v>-45000</v>
+        <v>2000</v>
       </c>
       <c r="F27" s="3">
-        <v>-688700</v>
+        <v>-3700</v>
       </c>
       <c r="G27" s="3">
-        <v>-23700</v>
+        <v>-51600</v>
       </c>
       <c r="H27" s="3">
-        <v>-22000</v>
+        <v>-21800</v>
       </c>
       <c r="I27" s="3">
+        <v>-172000</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-159600</v>
+      </c>
+      <c r="K27" s="3">
         <v>-23400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-62700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-2300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-13100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>12900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>16100</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1450,25 +1565,31 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-5500</v>
+        <v>1098800</v>
       </c>
       <c r="E29" s="3">
-        <v>-102600</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
+        <v>-414900</v>
+      </c>
+      <c r="F29" s="3">
+        <v>2600</v>
+      </c>
+      <c r="G29" s="3">
+        <v>-116200</v>
+      </c>
+      <c r="H29" s="3">
+        <v>-760900</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>8</v>
@@ -1479,17 +1600,23 @@
       <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1526,8 +1653,14 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1564,84 +1697,102 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>-2100</v>
+        <v>-600</v>
       </c>
       <c r="I32" s="3">
+        <v>21800</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="K32" s="3">
         <v>5500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>47500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-4300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-4600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-9900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1107400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-412900</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-167800</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-782700</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-172000</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-159600</v>
+      </c>
+      <c r="K33" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-62700</v>
+      </c>
+      <c r="M33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="N33" s="3">
         <v>-13100</v>
       </c>
-      <c r="E33" s="3">
-        <v>-147600</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-688700</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-23700</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-22000</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-23400</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-62700</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-13100</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>12900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>16100</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1678,89 +1829,107 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1107400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-412900</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-167800</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-782700</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-172000</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-159600</v>
+      </c>
+      <c r="K35" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-62700</v>
+      </c>
+      <c r="M35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="N35" s="3">
         <v>-13100</v>
       </c>
-      <c r="E35" s="3">
-        <v>-147600</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-688700</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-23700</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-22000</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-23400</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-62700</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-13100</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>12900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>16100</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45169</v>
+      </c>
+      <c r="E38" s="2">
+        <v>44985</v>
+      </c>
+      <c r="F38" s="2">
         <v>44804</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>44620</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44439</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44255</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44165</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44074</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>43982</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>43890</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>43799</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43708</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43616</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1775,8 +1944,10 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1791,84 +1962,98 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>27900</v>
+        <v>121100</v>
       </c>
       <c r="E41" s="3">
-        <v>25700</v>
+        <v>60900</v>
       </c>
       <c r="F41" s="3">
-        <v>4100</v>
+        <v>29400</v>
       </c>
       <c r="G41" s="3">
-        <v>72300</v>
+        <v>186200</v>
       </c>
       <c r="H41" s="3">
-        <v>110800</v>
+        <v>29600</v>
       </c>
       <c r="I41" s="3">
+        <v>523700</v>
+      </c>
+      <c r="J41" s="3">
+        <v>802200</v>
+      </c>
+      <c r="K41" s="3">
         <v>159900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>182300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>154100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>174000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>204300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>195400</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>11300</v>
+        <v>2100</v>
       </c>
       <c r="G42" s="3">
-        <v>57600</v>
+        <v>6800</v>
       </c>
       <c r="H42" s="3">
-        <v>64100</v>
+        <v>81600</v>
       </c>
       <c r="I42" s="3">
+        <v>417200</v>
+      </c>
+      <c r="J42" s="3">
+        <v>464000</v>
+      </c>
+      <c r="K42" s="3">
         <v>67200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>63000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>53500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>64900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>67000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>100700</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1878,35 +2063,41 @@
       <c r="E43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>13600</v>
+      <c r="F43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H43" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="I43" s="3">
+        <v>98700</v>
+      </c>
+      <c r="J43" s="3">
+        <v>9900</v>
+      </c>
+      <c r="K43" s="3">
         <v>100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2600</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1943,84 +2134,102 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>17300</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>22100</v>
+        <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>49000</v>
+        <v>18100</v>
       </c>
       <c r="G45" s="3">
-        <v>39800</v>
+        <v>159800</v>
       </c>
       <c r="H45" s="3">
-        <v>98200</v>
+        <v>355000</v>
       </c>
       <c r="I45" s="3">
+        <v>288400</v>
+      </c>
+      <c r="J45" s="3">
+        <v>711500</v>
+      </c>
+      <c r="K45" s="3">
         <v>73500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>118400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>108000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>62600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>85300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>119600</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>47200</v>
+        <v>121100</v>
       </c>
       <c r="E46" s="3">
-        <v>48700</v>
+        <v>60900</v>
       </c>
       <c r="F46" s="3">
-        <v>64400</v>
+        <v>49600</v>
       </c>
       <c r="G46" s="3">
-        <v>183400</v>
+        <v>352800</v>
       </c>
       <c r="H46" s="3">
-        <v>274500</v>
+        <v>466200</v>
       </c>
       <c r="I46" s="3">
+        <v>1328000</v>
+      </c>
+      <c r="J46" s="3">
+        <v>1987700</v>
+      </c>
+      <c r="K46" s="3">
         <v>300700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>366400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>318200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>301500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>356600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>415800</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2030,35 +2239,41 @@
       <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>247000</v>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H47" s="3">
-        <v>148800</v>
+        <v>0</v>
       </c>
       <c r="I47" s="3">
+        <v>1788900</v>
+      </c>
+      <c r="J47" s="3">
+        <v>1077600</v>
+      </c>
+      <c r="K47" s="3">
         <v>147500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>153700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>190600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>230300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>222000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>201700</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2069,34 +2284,40 @@
         <v>0</v>
       </c>
       <c r="F48" s="3">
-        <v>5100</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3">
-        <v>269400</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3">
-        <v>281800</v>
+        <v>37000</v>
       </c>
       <c r="I48" s="3">
+        <v>1950700</v>
+      </c>
+      <c r="J48" s="3">
+        <v>2041000</v>
+      </c>
+      <c r="K48" s="3">
         <v>284800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>295200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>325300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>362700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>83700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>82300</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2106,35 +2327,41 @@
       <c r="E49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>206800</v>
+      <c r="F49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H49" s="3">
-        <v>239100</v>
+        <v>0</v>
       </c>
       <c r="I49" s="3">
+        <v>1497600</v>
+      </c>
+      <c r="J49" s="3">
+        <v>1731600</v>
+      </c>
+      <c r="K49" s="3">
         <v>242900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>178800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>184300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>142200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>145000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>135000</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2171,8 +2398,14 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2209,46 +2442,58 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E52" s="3">
-        <v>2000</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G52" s="3">
-        <v>59400</v>
+        <v>14700</v>
       </c>
       <c r="H52" s="3">
-        <v>115700</v>
+        <v>0</v>
       </c>
       <c r="I52" s="3">
+        <v>430200</v>
+      </c>
+      <c r="J52" s="3">
+        <v>838000</v>
+      </c>
+      <c r="K52" s="3">
         <v>114700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>66100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>61800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>94000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>87500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>60300</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2285,46 +2530,58 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>47200</v>
+        <v>121100</v>
       </c>
       <c r="E54" s="3">
-        <v>50700</v>
+        <v>60900</v>
       </c>
       <c r="F54" s="3">
-        <v>69500</v>
+        <v>49600</v>
       </c>
       <c r="G54" s="3">
-        <v>965900</v>
+        <v>367500</v>
       </c>
       <c r="H54" s="3">
-        <v>1059900</v>
+        <v>503200</v>
       </c>
       <c r="I54" s="3">
+        <v>6995400</v>
+      </c>
+      <c r="J54" s="3">
+        <v>7675900</v>
+      </c>
+      <c r="K54" s="3">
         <v>1090600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1060100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1080200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1130700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>894700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>895200</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2339,8 +2596,10 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2355,8 +2614,10 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2384,169 +2645,199 @@
       <c r="K57" s="3">
         <v>0</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>8</v>
+      <c r="L57" s="3">
+        <v>0</v>
       </c>
       <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O57" s="3">
         <v>5500</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>62700</v>
+        <v>101900</v>
       </c>
       <c r="E58" s="3">
-        <v>86700</v>
+        <v>102700</v>
       </c>
       <c r="F58" s="3">
-        <v>139700</v>
+        <v>97000</v>
       </c>
       <c r="G58" s="3">
-        <v>141600</v>
+        <v>628200</v>
       </c>
       <c r="H58" s="3">
-        <v>154000</v>
+        <v>1012000</v>
       </c>
       <c r="I58" s="3">
+        <v>1025400</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1114900</v>
+      </c>
+      <c r="K58" s="3">
         <v>149800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>140800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>62000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>58300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>47400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>54800</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>694500</v>
+        <v>13200</v>
       </c>
       <c r="E59" s="3">
-        <v>669100</v>
+        <v>11900</v>
       </c>
       <c r="F59" s="3">
-        <v>511700</v>
+        <v>730100</v>
       </c>
       <c r="G59" s="3">
-        <v>575900</v>
+        <v>4845400</v>
       </c>
       <c r="H59" s="3">
-        <v>573700</v>
+        <v>3705600</v>
       </c>
       <c r="I59" s="3">
+        <v>4170800</v>
+      </c>
+      <c r="J59" s="3">
+        <v>4154900</v>
+      </c>
+      <c r="K59" s="3">
         <v>556700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>500800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>514500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>539200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>446700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>451600</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>757200</v>
+        <v>115100</v>
       </c>
       <c r="E60" s="3">
-        <v>755800</v>
+        <v>114600</v>
       </c>
       <c r="F60" s="3">
-        <v>651400</v>
+        <v>796000</v>
       </c>
       <c r="G60" s="3">
-        <v>717500</v>
+        <v>5473600</v>
       </c>
       <c r="H60" s="3">
-        <v>727700</v>
+        <v>4717600</v>
       </c>
       <c r="I60" s="3">
+        <v>5196200</v>
+      </c>
+      <c r="J60" s="3">
+        <v>5269900</v>
+      </c>
+      <c r="K60" s="3">
         <v>706500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>641600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>576600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>597600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>499600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>506400</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>33300</v>
+        <v>1200</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>49900</v>
+        <v>35000</v>
       </c>
       <c r="G61" s="3">
-        <v>98200</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>144200</v>
+        <v>361100</v>
       </c>
       <c r="I61" s="3">
+        <v>711500</v>
+      </c>
+      <c r="J61" s="3">
+        <v>1044600</v>
+      </c>
+      <c r="K61" s="3">
         <v>174400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>180100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>186100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>179900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>198300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>196900</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2554,37 +2845,43 @@
         <v>0</v>
       </c>
       <c r="E62" s="3">
-        <v>21400</v>
+        <v>0</v>
       </c>
       <c r="F62" s="3">
-        <v>6300</v>
+        <v>0</v>
       </c>
       <c r="G62" s="3">
-        <v>130300</v>
+        <v>154800</v>
       </c>
       <c r="H62" s="3">
-        <v>145700</v>
+        <v>45700</v>
       </c>
       <c r="I62" s="3">
+        <v>943400</v>
+      </c>
+      <c r="J62" s="3">
+        <v>1055200</v>
+      </c>
+      <c r="K62" s="3">
         <v>148700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>160400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>174800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>198000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>26200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>20500</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2621,8 +2918,14 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2659,8 +2962,14 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2697,46 +3006,58 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>786900</v>
+        <v>116400</v>
       </c>
       <c r="E66" s="3">
-        <v>772300</v>
+        <v>114600</v>
       </c>
       <c r="F66" s="3">
-        <v>709000</v>
+        <v>827400</v>
       </c>
       <c r="G66" s="3">
-        <v>949800</v>
+        <v>5592800</v>
       </c>
       <c r="H66" s="3">
-        <v>1022200</v>
+        <v>5134800</v>
       </c>
       <c r="I66" s="3">
+        <v>6878400</v>
+      </c>
+      <c r="J66" s="3">
+        <v>7402800</v>
+      </c>
+      <c r="K66" s="3">
         <v>1035300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>986800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>942400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>982600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>733700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>741900</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2751,8 +3072,10 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2789,8 +3112,14 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2827,8 +3156,14 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2865,8 +3200,14 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2903,46 +3244,58 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1550000</v>
+        <v>-946100</v>
       </c>
       <c r="E72" s="3">
-        <v>-1536900</v>
+        <v>-954600</v>
       </c>
       <c r="F72" s="3">
-        <v>-1389400</v>
+        <v>-1660000</v>
       </c>
       <c r="G72" s="3">
-        <v>-740200</v>
+        <v>-11130800</v>
       </c>
       <c r="H72" s="3">
-        <v>-711900</v>
+        <v>-10062000</v>
       </c>
       <c r="I72" s="3">
+        <v>-5360900</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-5155600</v>
+      </c>
+      <c r="K72" s="3">
         <v>-693600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-670200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-612400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-640100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-632600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-645500</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2979,8 +3332,14 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3017,8 +3376,14 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3055,46 +3420,58 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-739800</v>
+        <v>4800</v>
       </c>
       <c r="E76" s="3">
-        <v>-721500</v>
+        <v>-53700</v>
       </c>
       <c r="F76" s="3">
-        <v>-639500</v>
+        <v>-777800</v>
       </c>
       <c r="G76" s="3">
-        <v>16200</v>
+        <v>-5225300</v>
       </c>
       <c r="H76" s="3">
-        <v>37700</v>
+        <v>-4631600</v>
       </c>
       <c r="I76" s="3">
+        <v>117000</v>
+      </c>
+      <c r="J76" s="3">
+        <v>273100</v>
+      </c>
+      <c r="K76" s="3">
         <v>55300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>73300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>137800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>148100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>161000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>153300</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3131,89 +3508,107 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45169</v>
+      </c>
+      <c r="E80" s="2">
+        <v>44985</v>
+      </c>
+      <c r="F80" s="2">
         <v>44804</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>44620</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44439</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44255</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44165</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44074</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>43982</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>43890</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>43799</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43708</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43616</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1107400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-412900</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-167800</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-782700</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-172000</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-159600</v>
+      </c>
+      <c r="K81" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-62700</v>
+      </c>
+      <c r="M81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="N81" s="3">
         <v>-13100</v>
       </c>
-      <c r="E81" s="3">
-        <v>-147600</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-688700</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-23700</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-22000</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-23400</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-62700</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-13100</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>12900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>16100</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3228,31 +3623,33 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>8</v>
+      <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>23900</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>8</v>
@@ -3260,14 +3657,20 @@
       <c r="L83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O83" s="3">
         <v>25900</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3304,8 +3707,14 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3342,8 +3751,14 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3380,8 +3795,14 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3418,8 +3839,14 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3456,31 +3883,37 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>-77700</v>
-      </c>
-      <c r="E89" s="3">
-        <v>36000</v>
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F89" s="3">
-        <v>19100</v>
+        <v>-304800</v>
       </c>
       <c r="G89" s="3">
-        <v>17300</v>
-      </c>
-      <c r="H89" s="3">
-        <v>10000</v>
+        <v>261000</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>8</v>
+      <c r="J89" s="3">
+        <v>72400</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>8</v>
@@ -3488,14 +3921,20 @@
       <c r="L89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O89" s="3">
         <v>50900</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3510,13 +3949,15 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-20500</v>
+        <v>-3100</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -3536,20 +3977,26 @@
       <c r="J91" s="3">
         <v>0</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M91" s="3">
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O91" s="3">
         <v>-41800</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3586,8 +4033,14 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3624,31 +4077,37 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-400</v>
-      </c>
-      <c r="E94" s="3">
-        <v>11400</v>
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F94" s="3">
-        <v>-20400</v>
+        <v>-2900</v>
       </c>
       <c r="G94" s="3">
-        <v>14700</v>
-      </c>
-      <c r="H94" s="3">
-        <v>16800</v>
+        <v>82600</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>8</v>
+      <c r="J94" s="3">
+        <v>121800</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>8</v>
@@ -3656,14 +4115,20 @@
       <c r="L94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O94" s="3">
         <v>-205200</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3678,8 +4143,10 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3716,8 +4183,14 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3754,8 +4227,14 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3792,8 +4271,14 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3830,31 +4315,37 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>2400</v>
-      </c>
-      <c r="E100" s="3">
-        <v>19200</v>
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F100" s="3">
-        <v>-129100</v>
+        <v>17500</v>
       </c>
       <c r="G100" s="3">
-        <v>56300</v>
-      </c>
-      <c r="H100" s="3">
-        <v>20300</v>
+        <v>138800</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>8</v>
+      <c r="J100" s="3">
+        <v>146900</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>8</v>
@@ -3862,37 +4353,43 @@
       <c r="L100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O100" s="3">
         <v>145600</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>8</v>
+      <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
       </c>
       <c r="F101" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>8</v>
@@ -3900,37 +4397,43 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O101" s="3">
         <v>5000</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>8</v>
+      <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
       </c>
       <c r="F102" s="3">
-        <v>-132600</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>8</v>
@@ -3938,10 +4441,16 @@
       <c r="L102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M102" s="3">
+      <c r="M102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O102" s="3">
         <v>-3600</v>
       </c>
-      <c r="N102" s="3" t="s">
+      <c r="P102" s="3" t="s">
         <v>8</v>
       </c>
     </row>
